--- a/wiki/reports/daily/2026-10-02_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-02_일일보고.xlsx
@@ -95,7 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -613,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-02 07:57   |   전일: 10월 1일   |   월평균 기준: 이전 작업일 1일 평균   |   10월 누적 작업일: 2일</t>
+          <t>생성: 2026-10-02 16:00   |   전일: 10월 1일   |   월평균 기준: 이전 작업일 1일 평균   |   10월 누적 작업일: 2일</t>
         </is>
       </c>
     </row>
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>49</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-39</v>
+        <v>19</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.7959183673469388</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>49</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-39</v>
+        <v>19</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.7959183673469388</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3160</v>
+        <v>18368</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>13574</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-10414</v>
+        <v>4794</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.7672020038308531</v>
+        <v>0.3531751878591425</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>13574</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-10414</v>
+        <v>4794</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.7672020038308531</v>
+        <v>0.3531751878591425</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:52:40</t>
+          <t>5:06:08</t>
         </is>
       </c>
     </row>
@@ -737,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-36</v>
+        <v>14</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.972972972972973</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>37</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-36</v>
+        <v>14</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.972972972972973</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>314</v>
+        <v>17762</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>10835</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-10521</v>
+        <v>6927</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.9710198431010614</v>
+        <v>0.6393170281495154</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>10835</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-10521</v>
+        <v>6927</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.9710198431010614</v>
+        <v>0.6393170281495154</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:05:14</t>
+          <t>4:56:02</t>
         </is>
       </c>
     </row>
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>86</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-75</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.8720930232558139</v>
+        <v>0.3837209302325582</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>86</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-75</v>
+        <v>33</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.8720930232558139</v>
+        <v>0.3837209302325582</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -828,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3474</v>
+        <v>36130</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>24409</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-20935</v>
+        <v>11721</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.8576754475808104</v>
+        <v>0.4801917325576632</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>24409</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-20935</v>
+        <v>11721</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.8576754475808104</v>
+        <v>0.4801917325576632</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:57:54</t>
+          <t>10:02:10</t>
         </is>
       </c>
     </row>
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>86</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-75</v>
+        <v>33</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.8720930232558139</v>
+        <v>0.3837209302325582</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>86</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-75</v>
+        <v>33</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.8720930232558139</v>
+        <v>0.3837209302325582</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
@@ -891,13 +891,13 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>27883</v>
+        <v>60539</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>0179</t>
+          <t>0179 ㅋㅌ</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr"/>
@@ -1048,167 +1048,577 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>8216</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>2:16:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0153, 0179, 0107</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>2136</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>0:35:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>356</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>0:05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>1:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>18368</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>5:06:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="14" t="n">
-        <v>3160</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:52:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
+      <c r="E13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr"/>
+      <c r="I13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="J13" s="24" t="n">
+        <v>314</v>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>0:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr"/>
+      <c r="I14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>2950</v>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>0:49:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr"/>
+      <c r="I15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>0:03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr"/>
+      <c r="I16" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>1260</v>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>0:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr"/>
+      <c r="I17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>510</v>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>0:08:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>0106 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr"/>
+      <c r="I18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>488</v>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>0:08:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C19" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="D19" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>0068</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>314</v>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>0:05:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>12060</v>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>3:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>314</v>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>0:05:14</t>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>17762</v>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>4:56:02</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
